--- a/EXCEL/Exercise Files/Chapter06/06_06_Combinations Without Duplication.xlsx
+++ b/EXCEL/Exercise Files/Chapter06/06_06_Combinations Without Duplication.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter06\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0A891B-5EFD-43CE-9275-FE1D12FB5C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84535408-C942-4EAE-9679-B2BA11A2FD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{3120C202-D0C7-4531-A7A3-F2AE4479DFA3}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" xr2:uid="{3120C202-D0C7-4531-A7A3-F2AE4479DFA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -414,18 +413,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9486D335-CA52-43CC-AFE5-6581EB2E9E0F}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.84375" customWidth="1"/>
-    <col min="2" max="2" width="11.84375" customWidth="1"/>
+    <col min="1" max="1" width="31.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -433,7 +432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -441,9 +440,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>0</v>
+      </c>
+      <c r="B6">
+        <f>COMBIN(B3,B4)</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
